--- a/01_Data/Monkey/Parameters.xlsx
+++ b/01_Data/Monkey/Parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Modeling_Projects\APriori_PBPK\01_Data\Monkey\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KrinaMehta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A331D090-F25D-4E8A-B734-CC85EB2D404B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5D8EF8-E327-4055-A58D-35E56252756B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="87">
   <si>
     <t>Drug Name</t>
   </si>
@@ -197,9 +197,6 @@
     <t>TNFA</t>
   </si>
   <si>
-    <t>Benamara et al., 2025; PMID: 41536283</t>
-  </si>
-  <si>
     <t>Shealy et al., 2011; PMC3180089</t>
   </si>
   <si>
@@ -279,6 +276,12 @@
   </si>
   <si>
     <t>Ligand-binding receptor assay (assumed same across species)</t>
+  </si>
+  <si>
+    <t>Benamara et al., 2026</t>
+  </si>
+  <si>
+    <t>Benamara et al., 2026; PMID: 41536283</t>
   </si>
 </sst>
 </file>
@@ -747,7 +750,7 @@
         <v>11</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -784,13 +787,13 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>27</v>
@@ -885,7 +888,7 @@
         <v>11</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
@@ -922,13 +925,13 @@
         <v>9</v>
       </c>
       <c r="D14">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>27</v>
@@ -1023,7 +1026,7 @@
         <v>37</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
@@ -1158,7 +1161,7 @@
         <v>41</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -1195,13 +1198,13 @@
         <v>9</v>
       </c>
       <c r="D26">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>27</v>
@@ -1296,7 +1299,7 @@
         <v>48</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -1331,13 +1334,13 @@
         <v>9</v>
       </c>
       <c r="D32">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>27</v>
@@ -1432,7 +1435,7 @@
         <v>53</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -1469,13 +1472,13 @@
         <v>9</v>
       </c>
       <c r="D38">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="G38" t="s">
         <v>27</v>
@@ -1498,10 +1501,10 @@
         <v>10</v>
       </c>
       <c r="F39" t="s">
+        <v>58</v>
+      </c>
+      <c r="G39" t="s">
         <v>59</v>
-      </c>
-      <c r="G39" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
@@ -1521,10 +1524,10 @@
         <v>16</v>
       </c>
       <c r="F40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
@@ -1544,10 +1547,10 @@
         <v>18</v>
       </c>
       <c r="F41" t="s">
+        <v>61</v>
+      </c>
+      <c r="G41" t="s">
         <v>62</v>
-      </c>
-      <c r="G41" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
@@ -1567,10 +1570,10 @@
         <v>21</v>
       </c>
       <c r="F42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
@@ -1590,15 +1593,15 @@
         <v>18</v>
       </c>
       <c r="F43" t="s">
+        <v>63</v>
+      </c>
+      <c r="G43" t="s">
         <v>64</v>
-      </c>
-      <c r="G43" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B44" t="s">
         <v>57</v>
@@ -1607,13 +1610,13 @@
         <v>9</v>
       </c>
       <c r="D44">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="G44" t="s">
         <v>27</v>
@@ -1621,7 +1624,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B45" t="s">
         <v>57</v>
@@ -1636,15 +1639,15 @@
         <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G45" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
         <v>57</v>
@@ -1659,15 +1662,15 @@
         <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B47" t="s">
         <v>57</v>
@@ -1682,15 +1685,15 @@
         <v>18</v>
       </c>
       <c r="F47" t="s">
+        <v>61</v>
+      </c>
+      <c r="G47" t="s">
         <v>62</v>
-      </c>
-      <c r="G47" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B48" t="s">
         <v>57</v>
@@ -1705,15 +1708,15 @@
         <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B49" t="s">
         <v>57</v>
@@ -1728,10 +1731,10 @@
         <v>18</v>
       </c>
       <c r="F49" t="s">
+        <v>63</v>
+      </c>
+      <c r="G49" t="s">
         <v>64</v>
-      </c>
-      <c r="G49" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1770,10 +1773,10 @@
     </row>
     <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" t="s">
         <v>69</v>
-      </c>
-      <c r="B2" t="s">
-        <v>70</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -1785,7 +1788,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>12</v>
@@ -1793,10 +1796,10 @@
     </row>
     <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" t="s">
         <v>69</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -1808,7 +1811,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>12</v>
@@ -1816,10 +1819,10 @@
     </row>
     <row r="4" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" t="s">
         <v>69</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -1831,18 +1834,18 @@
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
         <v>69</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -1854,18 +1857,18 @@
         <v>10</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" t="s">
         <v>69</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
@@ -1877,18 +1880,18 @@
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" t="s">
         <v>69</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -1897,15 +1900,15 @@
         <v>0.12</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
         <v>43</v>
@@ -1928,7 +1931,7 @@
     </row>
     <row r="9" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
         <v>43</v>
@@ -1946,12 +1949,12 @@
         <v>44</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
         <v>43</v>
@@ -1969,12 +1972,12 @@
         <v>44</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="87" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
         <v>43</v>
@@ -1997,7 +2000,7 @@
     </row>
     <row r="12" spans="1:7" ht="87" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
         <v>43</v>
@@ -2020,7 +2023,7 @@
     </row>
     <row r="13" spans="1:7" ht="87" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13" t="s">
         <v>43</v>
@@ -2043,7 +2046,7 @@
     </row>
     <row r="14" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B14" t="s">
         <v>50</v>
@@ -2066,7 +2069,7 @@
     </row>
     <row r="15" spans="1:7" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B15" t="s">
         <v>50</v>
@@ -2075,7 +2078,7 @@
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -2089,7 +2092,7 @@
     </row>
     <row r="16" spans="1:7" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
         <v>50</v>
@@ -2098,7 +2101,7 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
         <v>16</v>
@@ -2112,7 +2115,7 @@
     </row>
     <row r="17" spans="1:7" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B17" t="s">
         <v>50</v>
@@ -2135,7 +2138,7 @@
     </row>
     <row r="18" spans="1:7" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s">
         <v>50</v>
@@ -2158,7 +2161,7 @@
     </row>
     <row r="19" spans="1:7" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
         <v>50</v>
